--- a/KatalonData/MultibillTestData/MultibillCCData.xlsx
+++ b/KatalonData/MultibillTestData/MultibillCCData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\MultibillTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{2BC165B1-800F-460B-A2DC-993864F6B38A}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{AA39726B-62B3-4FCF-BBA2-CEB1EAB08D28}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="10" firstSheet="6" windowHeight="15675" windowWidth="28995" xWindow="14303" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-2010"/>
+    <workbookView activeTab="1" windowHeight="13097" windowWidth="24686" xWindow="3394" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="3394"/>
   </bookViews>
   <sheets>
     <sheet name="CCData" r:id="rId1" sheetId="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="165">
   <si>
     <t>Result</t>
   </si>
@@ -400,124 +400,145 @@
     <t>$*.51</t>
   </si>
   <si>
-    <t>Wed Sep 17 23:54:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 23:55:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Sep 17 23:56:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 18 00:02:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 18 00:04:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 18 00:05:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Sep 18 00:06:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 19:08:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 19:28:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 19:41:09 EST 2025</t>
-  </si>
-  <si>
     <t>sm</t>
   </si>
   <si>
-    <t>Thu Nov 20 21:03:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 21:04:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 21:13:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 21:17:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu Nov 20 21:17:44 EST 2025</t>
-  </si>
-  <si>
     <t>Fri Nov 21 13:46:58 EST 2025</t>
   </si>
   <si>
-    <t>Fri Nov 21 19:53:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 20:20:19 EST 2025</t>
+    <t>Wed Dec 10 19:18:22 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:18:41 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:19:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:20:14 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:20:54 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:21:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:22:15 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:22:46 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:24:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:25:17 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:26:12 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:26:46 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:27:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:27:55 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:28:19 EST 2025</t>
+  </si>
+  <si>
+    <t>DECEMBER 31 ,2021</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 19:58:34 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 20:00:25 EST 2025</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Mon Nov 24 14:32:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 14:36:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 14:37:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 14:40:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 14:42:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 14:44:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 14:47:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 14:52:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 15:00:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 15:02:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 15:14:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 15:18:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 15:23:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 16:00:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 16:27:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 16:30:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 16:35:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 16:40:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 16:40:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 24 16:42:59 EST 2025</t>
+    <t>Wed Dec 10 20:05:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 20:06:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 20:07:24 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 20:29:35 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 20:30:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Wed Dec 10 20:30:58 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:46:54 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:47:25 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:51:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:51:24 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:51:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:51:59 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:52:35 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:53:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:53:36 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:53:53 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:54:50 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:55:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:55:32 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:57:04 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:58:00 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:58:56 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 14:59:31 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 15:00:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 15:00:40 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 15:01:05 EST 2025</t>
   </si>
 </sst>
 </file>
@@ -948,9 +969,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:26" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1030,7 +1051,7 @@
         <v>24</v>
       </c>
     </row>
-    <row ht="72.5" r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row ht="72.900000000000006" r="2" spans="1:26" x14ac:dyDescent="0.4">
       <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
@@ -1111,13 +1132,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A8BF27D-9E5B-43D3-A8C6-55BD0B2E602C}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="24.453125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="15.08984375" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="24.4609375" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="15.07421875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1135,13 +1156,13 @@
       </c>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -1152,13 +1173,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D7CF63-52CE-45A5-AAAD-49E5406A5D05}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="12.453125" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.1796875" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="12.4609375" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.15234375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1190,12 +1211,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="43.5" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="43.75" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1210,8 +1231,8 @@
       <c r="G2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="15">
-        <v>44561</v>
+      <c r="H2" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I2" s="5">
         <v>13.03</v>
@@ -1220,7 +1241,7 @@
         <v>684958</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1257,9 +1278,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BCD28-A901-4577-AC2B-4D8F84F5F4AB}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1291,12 +1312,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="43.5" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="43.75" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1311,8 +1332,8 @@
       <c r="G2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="15">
-        <v>44561</v>
+      <c r="H2" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I2" s="5">
         <v>13.03</v>
@@ -1329,9 +1350,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAB8D87-1612-4A54-9789-20EBA3899496}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1348,12 +1369,12 @@
         <v>45</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1363,12 +1384,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -1385,9 +1406,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C795593-D462-4484-9AA4-88FCDAFE3571}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1419,12 +1440,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="43.5" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="43.75" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1439,8 +1460,8 @@
       <c r="G2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="15">
-        <v>44561</v>
+      <c r="H2" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I2" s="5">
         <v>13.03</v>
@@ -1449,7 +1470,7 @@
         <v>684958</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1486,9 +1507,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922E2DF4-99DD-461B-8823-21A4F73EC265}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1520,12 +1541,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="58" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="58.3" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1540,8 +1561,8 @@
       <c r="G2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="15">
-        <v>44561</v>
+      <c r="H2" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I2" s="5">
         <v>13.03</v>
@@ -1558,14 +1579,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2F5DCD-3C8F-4880-BB50-8902A2B8FCEA}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="16.453125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.90625" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="7.6328125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="16.4609375" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.921875" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="7.61328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1597,12 +1618,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1635,16 +1656,16 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97872C09-914A-48DE-8F4E-FDB918E9AE67}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="5.6328125" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="12.08984375" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="16.453125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.90625" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="8.36328125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="5.61328125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="12.07421875" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="16.4609375" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" width="22.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1676,12 +1697,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1696,8 +1717,8 @@
       <c r="G2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="15">
-        <v>44561</v>
+      <c r="H2" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I2" s="8">
         <v>16.510000000000002</v>
@@ -1706,7 +1727,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1728,9 +1749,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC5830D-66D0-4550-8001-686B3F1A766F}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1762,12 +1783,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1792,7 +1813,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1814,9 +1835,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA84A4D-C922-4030-9CED-DABBEF75479D}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1848,12 +1869,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1878,7 +1899,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1900,16 +1921,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A683BE9-6249-421D-92CB-328DFD4DF946}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.90625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="5.6328125" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.36328125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.90625" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="7" width="9.1796875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.921875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="5.61328125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.3828125" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.921875" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="7" width="9.15234375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1941,12 +1962,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1961,8 +1982,8 @@
       <c r="G2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="15">
-        <v>44561</v>
+      <c r="H2" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I2" s="8">
         <v>16.510000000000002</v>
@@ -1971,7 +1992,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -2008,9 +2029,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12B0A87-644D-4675-93A2-DC39D9AADE64}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2042,12 +2063,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2072,7 +2093,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -2094,12 +2115,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051F4528-1B41-4D78-BCA4-48AC174370CB}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.90625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2131,12 +2152,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2161,7 +2182,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="5"/>
@@ -2178,12 +2199,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320D1D33-46D9-47A1-8D21-2F325C6EB804}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.90625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2215,12 +2236,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2245,7 +2266,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="H3" s="6" t="s">
         <v>55</v>
       </c>
@@ -2258,12 +2279,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869053C2-BECE-477A-A52F-F9A660E766F1}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.90625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2295,12 +2316,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2333,21 +2354,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB854B13-0493-48E8-AA80-CD6F2F5005DA}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="5.90625" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.90625" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="5.6328125" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="7.26953125" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="5.921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.921875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="5.61328125" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="7.23046875" collapsed="true"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="13.0" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="16.453125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="15.90625" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="8.08984375" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="7.54296875" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="13.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="16.4609375" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.921875" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="8.07421875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="7.53515625" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="13.921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2379,12 +2400,12 @@
         <v>53</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2417,19 +2438,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36947155-855C-418A-BB46-98E870DFBFDC}">
   <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="25.6328125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" width="12.81640625" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="23.36328125" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="17.90625" collapsed="true"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="23.36328125" collapsed="true"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="17.90625" collapsed="true"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="17.54296875" collapsed="true"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="14.7265625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.61328125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="12.84375" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="23.3828125" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="17.921875" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.921875" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="23.3828125" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="17.921875" collapsed="true"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="17.53515625" collapsed="true"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="14.69140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2485,7 +2507,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>56</v>
       </c>
@@ -2505,8 +2527,8 @@
       <c r="G2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="15">
-        <v>44561</v>
+      <c r="H2" s="15" t="s">
+        <v>135</v>
       </c>
       <c r="I2" s="8">
         <v>16.510000000000002</v>
@@ -2547,9 +2569,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E46036D-3E0A-4CA8-9437-AC70B02E484B}">
   <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2593,12 +2615,12 @@
         <v>81</v>
       </c>
     </row>
-    <row ht="145.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row ht="113.15" r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2646,12 +2668,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B0777A2-8D17-46EC-97AB-260FCB0FA79E}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="5.6328125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="5.61328125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row ht="29.15" r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2668,12 +2690,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2683,7 +2705,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>58</v>
       </c>

--- a/KatalonData/MultibillTestData/MultibillCCData.xlsx
+++ b/KatalonData/MultibillTestData/MultibillCCData.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="183">
   <si>
     <t>Result</t>
   </si>
@@ -539,6 +539,60 @@
   </si>
   <si>
     <t>Mon Dec 15 15:01:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:48:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:48:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:48:49 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:48:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:49:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:49:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:50:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:50:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:51:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:51:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:52:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:54:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:55:00 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:55:55 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:56:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:57:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:57:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 30 12:58:04 EST 2026</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1270,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1317,7 +1371,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1374,7 +1428,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1389,7 +1443,7 @@
         <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -1445,7 +1499,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1546,7 +1600,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1623,7 +1677,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1702,7 +1756,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1788,7 +1842,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1874,7 +1928,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1967,7 +2021,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2068,7 +2122,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2157,7 +2211,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2321,7 +2375,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2405,7 +2459,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2620,7 +2674,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2695,7 +2749,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/MultibillTestData/MultibillCCData.xlsx
+++ b/KatalonData/MultibillTestData/MultibillCCData.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="292">
   <si>
     <t>Result</t>
   </si>
@@ -593,6 +593,333 @@
   </si>
   <si>
     <t>Fri Jan 30 12:58:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 09 13:26:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:08:39 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:08:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:09:23 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:09:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:10:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:10:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:11:21 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:12:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:12:28 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:13:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:14:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:15:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:16:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:17:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:17:40 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:18:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:18:41 EST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 11 21:49:08 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:53:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:53:55 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:54:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:54:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:55:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:55:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:56:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:56:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:57:14 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:57:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:57:56 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 15:59:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 16:00:24 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 16:01:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 16:01:54 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 16:02:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 16:03:04 EST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 16:03:29 EST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 14 21:19:25 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:32:19 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:32:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:33:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:33:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:33:47 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:34:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:34:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:35:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:36:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:36:10 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:36:48 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:38:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:39:13 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:40:07 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:40:42 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:41:16 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:41:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:42:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:33:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:34:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:34:44 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:34:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:35:34 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:35:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:36:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:36:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:37:51 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:38:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:38:32 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:40:02 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:40:58 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:41:52 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:42:26 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:43:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:43:35 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 20 17:43:59 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:38:17 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:38:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:39:05 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:39:46 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:41:06 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:42:03 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:43:11 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:43:57 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:45:27 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:45:37 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:49:31 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 21:53:18 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 22:01:15 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 22:01:50 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 22:03:30 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 22:04:36 EST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 27 22:05:01 EST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 09 11:34:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:10:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:13:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:14:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:19:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:22:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:24:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:25:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:26:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:26:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:27:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:29:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:32:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:39:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:42:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 18:43:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 19:11:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 10:35:47 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1270,7 +1597,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1371,7 +1698,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>282</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1428,7 +1755,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>288</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1443,7 +1770,7 @@
         <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>289</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -1499,7 +1826,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>281</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1600,7 +1927,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>283</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1677,7 +2004,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>287</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1756,7 +2083,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>278</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1842,7 +2169,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>284</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1928,7 +2255,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>286</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2021,7 +2348,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>274</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2122,7 +2449,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>285</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2211,7 +2538,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>276</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2375,7 +2702,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>258</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2459,7 +2786,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>291</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2674,7 +3001,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2749,7 +3076,7 @@
         <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/MultibillTestData/MultibillCCData.xlsx
+++ b/KatalonData/MultibillTestData/MultibillCCData.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="312">
   <si>
     <t>Result</t>
   </si>
@@ -920,6 +920,66 @@
   </si>
   <si>
     <t>Thu Mar 12 10:35:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 12:55:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 13:24:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 14:44:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 14:45:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 14:45:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 14:50:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 14:57:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:02:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:05:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:07:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:08:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:11:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:16:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:20:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:24:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:25:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:26:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:35:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:35:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 15:36:56 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1349,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:26" x14ac:dyDescent="0.4">
@@ -1512,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A8BF27D-9E5B-43D3-A8C6-55BD0B2E602C}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="24.4609375" collapsed="true"/>
@@ -1553,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D7CF63-52CE-45A5-AAAD-49E5406A5D05}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" bestFit="true" customWidth="true" width="12.4609375" collapsed="true"/>
@@ -1593,11 +1653,11 @@
       </c>
     </row>
     <row ht="43.75" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>280</v>
+      <c r="B2" t="s" s="0">
+        <v>299</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1623,31 +1683,31 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>109</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>698</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>0</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="0">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="0">
         <v>697</v>
       </c>
     </row>
@@ -1658,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{176BCD28-A901-4577-AC2B-4D8F84F5F4AB}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
@@ -1694,11 +1754,11 @@
       </c>
     </row>
     <row ht="43.75" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>282</v>
+      <c r="B2" t="s" s="0">
+        <v>301</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1730,7 +1790,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAB8D87-1612-4A54-9789-20EBA3899496}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:5" x14ac:dyDescent="0.4">
@@ -1751,11 +1811,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>288</v>
+      <c r="B2" t="s" s="0">
+        <v>309</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1766,16 +1826,16 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>85</v>
       </c>
     </row>
@@ -1786,7 +1846,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C795593-D462-4484-9AA4-88FCDAFE3571}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
@@ -1822,11 +1882,11 @@
       </c>
     </row>
     <row ht="43.75" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>281</v>
+      <c r="B2" t="s" s="0">
+        <v>300</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1852,31 +1912,31 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="0">
         <v>0</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="0">
         <v>98</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="0">
         <v>789654</v>
       </c>
     </row>
@@ -1887,7 +1947,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922E2DF4-99DD-461B-8823-21A4F73EC265}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
@@ -1923,11 +1983,11 @@
       </c>
     </row>
     <row ht="58.3" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>283</v>
+      <c r="B2" t="s" s="0">
+        <v>302</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -1959,7 +2019,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2F5DCD-3C8F-4880-BB50-8902A2B8FCEA}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" bestFit="true" customWidth="true" width="16.4609375" collapsed="true"/>
@@ -2000,11 +2060,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>287</v>
+      <c r="B2" t="s" s="0">
+        <v>307</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2036,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97872C09-914A-48DE-8F4E-FDB918E9AE67}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="5.61328125" collapsed="true"/>
@@ -2079,11 +2139,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>278</v>
+      <c r="B2" t="s" s="0">
+        <v>298</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2109,16 +2169,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>46</v>
       </c>
     </row>
@@ -2129,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC5830D-66D0-4550-8001-686B3F1A766F}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
@@ -2165,11 +2225,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>284</v>
+      <c r="B2" t="s" s="0">
+        <v>304</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2195,16 +2255,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>115</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>57</v>
       </c>
     </row>
@@ -2215,7 +2275,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BA84A4D-C922-4030-9CED-DABBEF75479D}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
@@ -2251,11 +2311,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>286</v>
+      <c r="B2" t="s" s="0">
+        <v>306</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2281,16 +2341,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>112</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>98</v>
       </c>
     </row>
@@ -2301,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A683BE9-6249-421D-92CB-328DFD4DF946}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.921875" collapsed="true"/>
@@ -2344,11 +2404,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>274</v>
+      <c r="B2" t="s" s="0">
+        <v>308</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2374,10 +2434,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>113</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2409,7 +2469,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F12B0A87-644D-4675-93A2-DC39D9AADE64}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:10" x14ac:dyDescent="0.4">
@@ -2445,11 +2505,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>285</v>
+      <c r="B2" t="s" s="0">
+        <v>305</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2475,16 +2535,16 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>111</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>57</v>
       </c>
     </row>
@@ -2495,7 +2555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051F4528-1B41-4D78-BCA4-48AC174370CB}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.921875" collapsed="true"/>
@@ -2534,11 +2594,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>276</v>
+      <c r="B2" t="s" s="0">
+        <v>297</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2579,7 +2639,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320D1D33-46D9-47A1-8D21-2F325C6EB804}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="7" max="7" bestFit="true" customWidth="true" width="15.921875" collapsed="true"/>
@@ -2618,10 +2678,10 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>119</v>
       </c>
       <c r="C2" s="1"/>
@@ -2659,7 +2719,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{869053C2-BECE-477A-A52F-F9A660E766F1}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.921875" collapsed="true"/>
@@ -2698,11 +2758,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>258</v>
+      <c r="B2" t="s" s="0">
+        <v>296</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2734,7 +2794,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB854B13-0493-48E8-AA80-CD6F2F5005DA}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="5.921875" collapsed="true"/>
@@ -2782,11 +2842,11 @@
       </c>
     </row>
     <row ht="29.15" r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>291</v>
+      <c r="B2" t="s" s="0">
+        <v>294</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -2818,7 +2878,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36947155-855C-418A-BB46-98E870DFBFDC}">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="25.61328125" collapsed="true"/>
@@ -2949,7 +3009,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E46036D-3E0A-4CA8-9437-AC70B02E484B}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row ht="29.15" r="1" spans="1:15" x14ac:dyDescent="0.4">
@@ -2997,11 +3057,11 @@
       </c>
     </row>
     <row ht="113.15" r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>272</v>
+      <c r="B2" t="s" s="0">
+        <v>311</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -3048,7 +3108,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B0777A2-8D17-46EC-97AB-260FCB0FA79E}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" bestFit="true" customWidth="true" width="5.61328125" collapsed="true"/>
@@ -3072,11 +3132,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="B2" t="s">
-        <v>273</v>
+      <c r="B2" t="s" s="0">
+        <v>303</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
@@ -3087,16 +3147,16 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>58</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>116</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" t="s" s="0">
         <v>85</v>
       </c>
     </row>
